--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0010_ses-01_pet_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0010_ses-01_pet_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -752,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="BS2" s="0">
-        <v>0.0080778706732905214</v>
+        <v>0.0080778706732905215</v>
       </c>
       <c r="BT2" s="0">
         <v>0.02967862291189689</v>
@@ -973,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="X3" s="0">
-        <v>0.037900322152738294</v>
+        <v>0.037900322152738295</v>
       </c>
       <c r="Y3" s="0">
         <v>0</v>
@@ -1114,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="BS3" s="0">
-        <v>0.0080778706732905214</v>
+        <v>0.0080778706732905215</v>
       </c>
       <c r="BT3" s="0">
         <v>0.038158229458153142</v>
@@ -1446,7 +1447,7 @@
         <v>0.1506024096385542</v>
       </c>
       <c r="BI4" s="0">
-        <v>0.16496324188631883</v>
+        <v>0.16496324188631884</v>
       </c>
       <c r="BJ4" s="0">
         <v>0.014741109268472453</v>
@@ -1691,13 +1692,13 @@
         <v>0</v>
       </c>
       <c r="V5" s="0">
-        <v>0.030637254901960786</v>
+        <v>0.030637254901960787</v>
       </c>
       <c r="W5" s="0">
         <v>0.034188034188034191</v>
       </c>
       <c r="X5" s="0">
-        <v>0.037900322152738294</v>
+        <v>0.037900322152738295</v>
       </c>
       <c r="Y5" s="0">
         <v>0</v>
@@ -1817,7 +1818,7 @@
         <v>0.013737207225771</v>
       </c>
       <c r="BL5" s="0">
-        <v>0.26111323398293212</v>
+        <v>0.26111323398293213</v>
       </c>
       <c r="BM5" s="0">
         <v>0.028970392259111192</v>
@@ -1898,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="CM5" s="0">
-        <v>0.018632383081796162</v>
+        <v>0.018632383081796163</v>
       </c>
       <c r="CN5" s="0">
         <v>0.083752093802345065</v>
@@ -2140,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="AY6" s="0">
-        <v>0.020222446916076844</v>
+        <v>0.020222446916076845</v>
       </c>
       <c r="AZ6" s="0">
         <v>0.067926392491046067</v>
@@ -2167,7 +2168,7 @@
         <v>0.0061614294516327784</v>
       </c>
       <c r="BH6" s="0">
-        <v>0.22869254796965643</v>
+        <v>0.22869254796965644</v>
       </c>
       <c r="BI6" s="0">
         <v>0.27254796485565719</v>
@@ -2203,7 +2204,7 @@
         <v>0.01211680600993578</v>
       </c>
       <c r="BT6" s="0">
-        <v>0.097515475281946914</v>
+        <v>0.097515475281946915</v>
       </c>
       <c r="BU6" s="0">
         <v>0.010361620557455186</v>
@@ -2245,7 +2246,7 @@
         <v>0.082727648762039835</v>
       </c>
       <c r="CH6" s="0">
-        <v>0.083918554834150449</v>
+        <v>0.08391855483415045</v>
       </c>
       <c r="CI6" s="0">
         <v>0.022185246810870772</v>
@@ -2562,7 +2563,7 @@
         <v>0.0080729797368208605</v>
       </c>
       <c r="BS7" s="0">
-        <v>0.0080778706732905214</v>
+        <v>0.0080778706732905215</v>
       </c>
       <c r="BT7" s="0">
         <v>0.10599508182820318</v>
@@ -2864,7 +2865,7 @@
         <v>0.010128633647320976</v>
       </c>
       <c r="AY8" s="0">
-        <v>0.020222446916076844</v>
+        <v>0.020222446916076845</v>
       </c>
       <c r="AZ8" s="0">
         <v>0.049401012720760779</v>
@@ -3193,7 +3194,7 @@
         <v>0.092678405931417893</v>
       </c>
       <c r="AN9" s="0">
-        <v>0.17383746197305502</v>
+        <v>0.17383746197305503</v>
       </c>
       <c r="AO9" s="0">
         <v>0.029962546816479377</v>
@@ -3277,7 +3278,7 @@
         <v>0.011257458065968695</v>
       </c>
       <c r="BP9" s="0">
-        <v>0.02204585537918869</v>
+        <v>0.022045855379188691</v>
       </c>
       <c r="BQ9" s="0">
         <v>0.023929169657812853</v>
@@ -3627,7 +3628,7 @@
         <v>0.054948828903084057</v>
       </c>
       <c r="BL10" s="0">
-        <v>0.47764615972487628</v>
+        <v>0.47764615972487629</v>
       </c>
       <c r="BM10" s="0">
         <v>0.028970392259111216</v>
@@ -3660,7 +3661,7 @@
         <v>0</v>
       </c>
       <c r="BW10" s="0">
-        <v>0.087719298245614113</v>
+        <v>0.087719298245614114</v>
       </c>
       <c r="BX10" s="0">
         <v>0.22437245828074626</v>
@@ -3714,7 +3715,7 @@
         <v>0.43072505384063214</v>
       </c>
       <c r="CO10" s="0">
-        <v>0.079344088865379594</v>
+        <v>0.079344088865379595</v>
       </c>
       <c r="CP10" s="0">
         <v>0.36375264819922487</v>
@@ -3887,7 +3888,7 @@
         <v>0.28368794326241109</v>
       </c>
       <c r="AD11" s="0">
-        <v>0.071377587437544548</v>
+        <v>0.071377587437544549</v>
       </c>
       <c r="AE11" s="0">
         <v>0</v>
@@ -3917,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="AN11" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO11" s="0">
         <v>0.059925093632958754</v>
@@ -4264,7 +4265,7 @@
         <v>0.015857913098636236</v>
       </c>
       <c r="AI12" s="0">
-        <v>0.24323502584372172</v>
+        <v>0.24323502584372173</v>
       </c>
       <c r="AJ12" s="0">
         <v>0.74303405572755499</v>
@@ -4291,7 +4292,7 @@
         <v>0.18597997138769687</v>
       </c>
       <c r="AR12" s="0">
-        <v>0.087227414330218161</v>
+        <v>0.087227414330218162</v>
       </c>
       <c r="AS12" s="0">
         <v>0.066137566137566203</v>
@@ -4330,7 +4331,7 @@
         <v>0.17129153819801318</v>
       </c>
       <c r="BE12" s="0">
-        <v>0.04688232536333807</v>
+        <v>0.046882325363338071</v>
       </c>
       <c r="BF12" s="0">
         <v>0</v>
@@ -4378,7 +4379,7 @@
         <v>0.37310268803527552</v>
       </c>
       <c r="BU12" s="0">
-        <v>0.08289296445964156</v>
+        <v>0.082892964459641561</v>
       </c>
       <c r="BV12" s="0">
         <v>0</v>
@@ -4441,7 +4442,7 @@
         <v>0.10138411355020728</v>
       </c>
       <c r="CP12" s="0">
-        <v>0.44769556701443058</v>
+        <v>0.44769556701443059</v>
       </c>
       <c r="CQ12" s="0">
         <v>0</v>
@@ -4608,7 +4609,7 @@
         <v>0.10218679746576734</v>
       </c>
       <c r="AC13" s="0">
-        <v>0.59101654846335649</v>
+        <v>0.5910165484633565</v>
       </c>
       <c r="AD13" s="0">
         <v>0.19034023316678547</v>
@@ -4650,7 +4651,7 @@
         <v>0.39735099337748314</v>
       </c>
       <c r="AQ13" s="0">
-        <v>0.2288984263233188</v>
+        <v>0.22889842632331881</v>
       </c>
       <c r="AR13" s="0">
         <v>0.13707165109034256</v>
@@ -4710,7 +4711,7 @@
         <v>0.1547816473189606</v>
       </c>
       <c r="BK13" s="0">
-        <v>0.068686036128854946</v>
+        <v>0.068686036128854947</v>
       </c>
       <c r="BL13" s="0">
         <v>0.90434339574576406</v>
@@ -4758,13 +4759,13 @@
         <v>0.15797788309636637</v>
       </c>
       <c r="CA13" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB13" s="0">
         <v>0.10498687664041985</v>
       </c>
       <c r="CC13" s="0">
-        <v>0.24996875390576156</v>
+        <v>0.24996875390576157</v>
       </c>
       <c r="CD13" s="0">
         <v>0.064102564102564055</v>
@@ -4958,7 +4959,7 @@
         <v>0.15160128861095334</v>
       </c>
       <c r="Y14" s="0">
-        <v>0.078616352201257927</v>
+        <v>0.078616352201257928</v>
       </c>
       <c r="Z14" s="0">
         <v>0.022878059940517066</v>
@@ -4973,10 +4974,10 @@
         <v>0.78014184397163189</v>
       </c>
       <c r="AD14" s="0">
-        <v>0.095170116583392902</v>
+        <v>0.095170116583392903</v>
       </c>
       <c r="AE14" s="0">
-        <v>0.068306010928961824</v>
+        <v>0.068306010928961825</v>
       </c>
       <c r="AF14" s="0">
         <v>0.21052631578947389</v>
@@ -5054,7 +5055,7 @@
         <v>0.21240150736553637</v>
       </c>
       <c r="BE14" s="0">
-        <v>0.04688232536333807</v>
+        <v>0.046882325363338071</v>
       </c>
       <c r="BF14" s="0">
         <v>0.05553241704845209</v>
@@ -5153,7 +5154,7 @@
         <v>0.034057045551298459</v>
       </c>
       <c r="CL14" s="0">
-        <v>0.031577617784514365</v>
+        <v>0.031577617784514366</v>
       </c>
       <c r="CM14" s="0">
         <v>0.14905906465436944</v>
@@ -5458,7 +5459,7 @@
         <v>0.088802777105029387</v>
       </c>
       <c r="BS15" s="0">
-        <v>0.1292459307726482</v>
+        <v>0.12924593077264821</v>
       </c>
       <c r="BT15" s="0">
         <v>0.50453658950224667</v>
@@ -5482,7 +5483,7 @@
         <v>0.14481305950500251</v>
       </c>
       <c r="CA15" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB15" s="0">
         <v>0.10498687664041985</v>
@@ -5709,10 +5710,10 @@
         <v>0.98838086615361498</v>
       </c>
       <c r="AH16" s="0">
-        <v>0.039644782746590584</v>
+        <v>0.039644782746590585</v>
       </c>
       <c r="AI16" s="0">
-        <v>0.47633525894395506</v>
+        <v>0.47633525894395507</v>
       </c>
       <c r="AJ16" s="0">
         <v>1.1042311661506719</v>
@@ -5733,7 +5734,7 @@
         <v>0.22471910112359572</v>
       </c>
       <c r="AP16" s="0">
-        <v>0.4415011037527598</v>
+        <v>0.44150110375275981</v>
       </c>
       <c r="AQ16" s="0">
         <v>0.44349070100143101</v>
@@ -5814,7 +5815,7 @@
         <v>0.16166960611405071</v>
       </c>
       <c r="BQ16" s="0">
-        <v>0.083752093802345134</v>
+        <v>0.083752093802345135</v>
       </c>
       <c r="BR16" s="0">
         <v>0.14531363526277563</v>
@@ -6107,7 +6108,7 @@
         <v>0.13227513227513216</v>
       </c>
       <c r="AT17" s="0">
-        <v>0.44518642181413431</v>
+        <v>0.44518642181413432</v>
       </c>
       <c r="AU17" s="0">
         <v>0.055637982195845648</v>
@@ -6206,7 +6207,7 @@
         <v>0.35545023696682437</v>
       </c>
       <c r="CA17" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB17" s="0">
         <v>0.15748031496062978</v>
@@ -6227,7 +6228,7 @@
         <v>0.5731844235655611</v>
       </c>
       <c r="CH17" s="0">
-        <v>0.61834724614637115</v>
+        <v>0.61834724614637116</v>
       </c>
       <c r="CI17" s="0">
         <v>0.19966722129783676</v>
@@ -6245,7 +6246,7 @@
         <v>0.2049562138997576</v>
       </c>
       <c r="CN17" s="0">
-        <v>0.93323761665470117</v>
+        <v>0.93323761665470118</v>
       </c>
       <c r="CO17" s="0">
         <v>0.25566428634400051</v>
@@ -6370,7 +6371,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N18" s="0">
         <v>0</v>
@@ -6469,7 +6470,7 @@
         <v>0</v>
       </c>
       <c r="AT18" s="0">
-        <v>0.44518642181413431</v>
+        <v>0.44518642181413432</v>
       </c>
       <c r="AU18" s="0">
         <v>0.024727992087042513</v>
@@ -6541,7 +6542,7 @@
         <v>0.17946877243359641</v>
       </c>
       <c r="BR18" s="0">
-        <v>0.23411641236780475</v>
+        <v>0.23411641236780476</v>
       </c>
       <c r="BS18" s="0">
         <v>0.32311482693162058</v>
@@ -6589,7 +6590,7 @@
         <v>0.56136618802812688</v>
       </c>
       <c r="CH18" s="0">
-        <v>0.71551609911222946</v>
+        <v>0.71551609911222947</v>
       </c>
       <c r="CI18" s="0">
         <v>0.22185246810870751</v>
@@ -6699,13 +6700,13 @@
         <v>0.012075836251660463</v>
       </c>
       <c r="B19" s="0">
-        <v>0.0083626024418799356</v>
+        <v>0.0083626024418799357</v>
       </c>
       <c r="C19" s="0">
         <v>0.0088378258948298982</v>
       </c>
       <c r="D19" s="0">
-        <v>0.030052181515176433</v>
+        <v>0.030052181515176434</v>
       </c>
       <c r="E19" s="0">
         <v>0.015574868392362129</v>
@@ -6747,7 +6748,7 @@
         <v>0</v>
       </c>
       <c r="R19" s="0">
-        <v>0.045913682277318769</v>
+        <v>0.04591368227731877</v>
       </c>
       <c r="S19" s="0">
         <v>0.032506733537661467</v>
@@ -6765,7 +6766,7 @@
         <v>0.42735042735042855</v>
       </c>
       <c r="X19" s="0">
-        <v>0.47375402690923007</v>
+        <v>0.47375402690923008</v>
       </c>
       <c r="Y19" s="0">
         <v>0.13102725366876347</v>
@@ -6801,7 +6802,7 @@
         <v>0.64862673558325912</v>
       </c>
       <c r="AJ19" s="0">
-        <v>1.1558307533539764</v>
+        <v>1.1558307533539765</v>
       </c>
       <c r="AK19" s="0">
         <v>0.21543718891612867</v>
@@ -6819,7 +6820,7 @@
         <v>0.25468164794007564</v>
       </c>
       <c r="AP19" s="0">
-        <v>1.0154525386313495</v>
+        <v>1.0154525386313496</v>
       </c>
       <c r="AQ19" s="0">
         <v>0.55793991416309174</v>
@@ -7226,7 +7227,7 @@
         <v>0.58239122987324365</v>
       </c>
       <c r="BE20" s="0">
-        <v>0.20315674324113125</v>
+        <v>0.20315674324113126</v>
       </c>
       <c r="BF20" s="0">
         <v>0.18048035540746893</v>
@@ -7456,7 +7457,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N21" s="0">
         <v>0.031152647975077854</v>
@@ -7633,10 +7634,10 @@
         <v>0.40793246900117097</v>
       </c>
       <c r="BT21" s="0">
-        <v>0.90307809717629028</v>
+        <v>0.90307809717629029</v>
       </c>
       <c r="BU21" s="0">
-        <v>0.34193347839602078</v>
+        <v>0.34193347839602079</v>
       </c>
       <c r="BV21" s="0">
         <v>0.11466011466011455</v>
@@ -7645,7 +7646,7 @@
         <v>0.46783625730994111</v>
       </c>
       <c r="BX21" s="0">
-        <v>0.77128032534006385</v>
+        <v>0.77128032534006386</v>
       </c>
       <c r="BY21" s="0">
         <v>0.11148272017837225</v>
@@ -7953,13 +7954,13 @@
         <v>0.23441162681668989</v>
       </c>
       <c r="BF22" s="0">
-        <v>0.2637789809801469</v>
+        <v>0.26377898098014691</v>
       </c>
       <c r="BG22" s="0">
         <v>0.56069008009858234</v>
       </c>
       <c r="BH22" s="0">
-        <v>1.3498438197233364</v>
+        <v>1.3498438197233365</v>
       </c>
       <c r="BI22" s="0">
         <v>1.4308768154921987</v>
@@ -8034,7 +8035,7 @@
         <v>0.23028209556706944</v>
       </c>
       <c r="CG22" s="0">
-        <v>1.0518229628316484</v>
+        <v>1.0518229628316485</v>
       </c>
       <c r="CH22" s="0">
         <v>0.88776997482443276</v>
@@ -8189,7 +8190,7 @@
         <v>0.0065915233010348882</v>
       </c>
       <c r="P23" s="0">
-        <v>0.039811181254621054</v>
+        <v>0.039811181254621055</v>
       </c>
       <c r="Q23" s="0">
         <v>0.051440329218107136</v>
@@ -8300,7 +8301,7 @@
         <v>0.95096949487464766</v>
       </c>
       <c r="BA23" s="0">
-        <v>0.20970955227010651</v>
+        <v>0.20970955227010652</v>
       </c>
       <c r="BB23" s="0">
         <v>0.88704908338261634</v>
@@ -8324,7 +8325,7 @@
         <v>1.2717536813922392</v>
       </c>
       <c r="BI23" s="0">
-        <v>1.2372243141473946</v>
+        <v>1.2372243141473947</v>
       </c>
       <c r="BJ23" s="0">
         <v>0.62649714391008104</v>
@@ -8357,7 +8358,7 @@
         <v>0.56545094713033794</v>
       </c>
       <c r="BT23" s="0">
-        <v>1.1447468837445975</v>
+        <v>1.1447468837445976</v>
       </c>
       <c r="BU23" s="0">
         <v>0.62169723344731287</v>
@@ -8417,7 +8418,7 @@
         <v>0.67076579094466371</v>
       </c>
       <c r="CN23" s="0">
-        <v>1.244316822206273</v>
+        <v>1.2443168222062731</v>
       </c>
       <c r="CO23" s="0">
         <v>0.59948867142731366</v>
@@ -8459,7 +8460,7 @@
         <v>0.64841498559077992</v>
       </c>
       <c r="DB23" s="0">
-        <v>0.26123301985371022</v>
+        <v>0.26123301985371023</v>
       </c>
       <c r="DC23" s="0">
         <v>0.47897021403981571</v>
@@ -8489,7 +8490,7 @@
         <v>0</v>
       </c>
       <c r="DL23" s="0">
-        <v>0.17406440382941737</v>
+        <v>0.17406440382941738</v>
       </c>
       <c r="DM23" s="0">
         <v>0</v>
@@ -8518,7 +8519,7 @@
         <v>0.095620577548288316</v>
       </c>
       <c r="E24" s="0">
-        <v>0.065414447247920698</v>
+        <v>0.065414447247920699</v>
       </c>
       <c r="F24" s="0">
         <v>0.043040371868812911</v>
@@ -8527,7 +8528,7 @@
         <v>0.053418803418803368</v>
       </c>
       <c r="H24" s="0">
-        <v>0.050459178524573572</v>
+        <v>0.050459178524573573</v>
       </c>
       <c r="I24" s="0">
         <v>0.044296788482834956</v>
@@ -8572,7 +8573,7 @@
         <v>0.90379901960784237</v>
       </c>
       <c r="W24" s="0">
-        <v>0.75213675213675157</v>
+        <v>0.75213675213675158</v>
       </c>
       <c r="X24" s="0">
         <v>0.92855789274208755</v>
@@ -8689,7 +8690,7 @@
         <v>1.4272906580598874</v>
       </c>
       <c r="BJ24" s="0">
-        <v>0.71862907683803134</v>
+        <v>0.71862907683803135</v>
       </c>
       <c r="BK24" s="0">
         <v>0.570094099869496</v>
@@ -8704,7 +8705,7 @@
         <v>0.50708889578805705</v>
       </c>
       <c r="BO24" s="0">
-        <v>0.33772374197906085</v>
+        <v>0.33772374197906086</v>
       </c>
       <c r="BP24" s="0">
         <v>0.78630217519106338</v>
@@ -8764,7 +8765,7 @@
         <v>1.1527759374585917</v>
       </c>
       <c r="CI24" s="0">
-        <v>0.62118691070438103</v>
+        <v>0.62118691070438104</v>
       </c>
       <c r="CJ24" s="0">
         <v>0.53763440860215006</v>
@@ -8776,7 +8777,7 @@
         <v>0.25893646583301733</v>
       </c>
       <c r="CM24" s="0">
-        <v>0.96888392025339964</v>
+        <v>0.96888392025339965</v>
       </c>
       <c r="CN24" s="0">
         <v>1.2682459918640812</v>
@@ -8976,7 +8977,7 @@
         <v>1.4138286893704839</v>
       </c>
       <c r="AK25" s="0">
-        <v>0.6240249609984394</v>
+        <v>0.62402496099843941</v>
       </c>
       <c r="AL25" s="0">
         <v>0.46430644225188583</v>
@@ -9120,7 +9121,7 @@
         <v>0.28785261945883683</v>
       </c>
       <c r="CG25" s="0">
-        <v>1.0518229628316484</v>
+        <v>1.0518229628316485</v>
       </c>
       <c r="CH25" s="0">
         <v>1.2190274281171314</v>
@@ -9204,7 +9205,7 @@
         <v>0</v>
       </c>
       <c r="DI25" s="0">
-        <v>2.4922118380062281</v>
+        <v>2.4922118380062282</v>
       </c>
       <c r="DJ25" s="0">
         <v>0</v>
@@ -9302,7 +9303,7 @@
         <v>1.2317604699639935</v>
       </c>
       <c r="Y26" s="0">
-        <v>0.44549266247379415</v>
+        <v>0.44549266247379416</v>
       </c>
       <c r="Z26" s="0">
         <v>0.11439029970258512</v>
@@ -9326,7 +9327,7 @@
         <v>1.2631578947368411</v>
       </c>
       <c r="AG26" s="0">
-        <v>1.1468236004225127</v>
+        <v>1.1468236004225128</v>
       </c>
       <c r="AH26" s="0">
         <v>0.66603235014272066</v>
@@ -9440,7 +9441,7 @@
         <v>0.84766287236618965</v>
       </c>
       <c r="BS26" s="0">
-        <v>0.94511086877499006</v>
+        <v>0.94511086877499007</v>
       </c>
       <c r="BT26" s="0">
         <v>1.3440176375816149</v>
@@ -9542,13 +9543,13 @@
         <v>0.42725083508117728</v>
       </c>
       <c r="DA26" s="0">
-        <v>2.0893371757925054</v>
+        <v>2.0893371757925055</v>
       </c>
       <c r="DB26" s="0">
         <v>0.96656217345872431</v>
       </c>
       <c r="DC26" s="0">
-        <v>1.8111061218380466</v>
+        <v>1.8111061218380467</v>
       </c>
       <c r="DD26" s="0">
         <v>0.23679417122040053</v>
@@ -9850,10 +9851,10 @@
         <v>1.289695684819574</v>
       </c>
       <c r="CI27" s="0">
-        <v>0.97615085967831305</v>
+        <v>0.97615085967831306</v>
       </c>
       <c r="CJ27" s="0">
-        <v>0.81172253847775599</v>
+        <v>0.811722538477756</v>
       </c>
       <c r="CK27" s="0">
         <v>0.48531289910600212</v>
@@ -9862,7 +9863,7 @@
         <v>0.50208412277377745</v>
       </c>
       <c r="CM27" s="0">
-        <v>0.96888392025339964</v>
+        <v>0.96888392025339965</v>
       </c>
       <c r="CN27" s="0">
         <v>1.5314668581000226</v>
@@ -9907,7 +9908,7 @@
         <v>2.7377521613832827</v>
       </c>
       <c r="DB27" s="0">
-        <v>1.41065830721003</v>
+        <v>1.4106583072100301</v>
       </c>
       <c r="DC27" s="0">
         <v>2.7989821882951631</v>
@@ -9943,7 +9944,7 @@
         <v>0</v>
       </c>
       <c r="DN27" s="0">
-        <v>0.58593749999999944</v>
+        <v>0.58593749999999945</v>
       </c>
       <c r="DO27" s="0">
         <v>0</v>
@@ -9978,7 +9979,7 @@
         <v>0.090826521344232775</v>
       </c>
       <c r="I28" s="0">
-        <v>0.083056478405315839</v>
+        <v>0.08305647840531584</v>
       </c>
       <c r="J28" s="0">
         <v>0.22379947566980049</v>
@@ -10008,7 +10009,7 @@
         <v>0.13774104683195632</v>
       </c>
       <c r="S28" s="0">
-        <v>0.20897185845639515</v>
+        <v>0.20897185845639516</v>
       </c>
       <c r="T28" s="0">
         <v>0.068292016663252256</v>
@@ -10041,7 +10042,7 @@
         <v>1.4420803782505951</v>
       </c>
       <c r="AD28" s="0">
-        <v>1.0706638115631721</v>
+        <v>1.0706638115631722</v>
       </c>
       <c r="AE28" s="0">
         <v>0.4781420765027336</v>
@@ -10065,7 +10066,7 @@
         <v>1.0103261273308104</v>
       </c>
       <c r="AL28" s="0">
-        <v>0.60617785516218647</v>
+        <v>0.60617785516218648</v>
       </c>
       <c r="AM28" s="0">
         <v>1.2357120790855765</v>
@@ -10086,7 +10087,7 @@
         <v>1.1713395638629316</v>
       </c>
       <c r="AS28" s="0">
-        <v>0.72751322751322955</v>
+        <v>0.72751322751322956</v>
       </c>
       <c r="AT28" s="0">
         <v>0.94602114635503887</v>
@@ -10146,7 +10147,7 @@
         <v>1.0699273977837249</v>
       </c>
       <c r="BM28" s="0">
-        <v>0.96181702300249416</v>
+        <v>0.96181702300249417</v>
       </c>
       <c r="BN28" s="0">
         <v>0.72441270826865567</v>
@@ -10248,7 +10249,7 @@
         <v>0</v>
       </c>
       <c r="CU28" s="0">
-        <v>2.1956087824351362</v>
+        <v>2.1956087824351363</v>
       </c>
       <c r="CV28" s="0">
         <v>1.5547263681592085</v>
@@ -10287,7 +10288,7 @@
         <v>1.4227642276422805</v>
       </c>
       <c r="DH28" s="0">
-        <v>0.35650623885918103</v>
+        <v>0.35650623885918104</v>
       </c>
       <c r="DI28" s="0">
         <v>2.4922118380062375</v>
@@ -10331,7 +10332,7 @@
         <v>0.19935831542223451</v>
       </c>
       <c r="F29" s="0">
-        <v>0.16068405497690152</v>
+        <v>0.16068405497690153</v>
       </c>
       <c r="G29" s="0">
         <v>0.29380341880341854</v>
@@ -10358,7 +10359,7 @@
         <v>0.20768431983385235</v>
       </c>
       <c r="O29" s="0">
-        <v>0.098872849515522956</v>
+        <v>0.098872849515522957</v>
       </c>
       <c r="P29" s="0">
         <v>0.24455439913552843</v>
@@ -10409,10 +10410,10 @@
         <v>0.20491803278688506</v>
       </c>
       <c r="AF29" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="AG29" s="0">
-        <v>1.1241889240983844</v>
+        <v>1.1241889240983845</v>
       </c>
       <c r="AH29" s="0">
         <v>0.81668252457976465</v>
@@ -10526,7 +10527,7 @@
         <v>0.86380883183983137</v>
       </c>
       <c r="BS29" s="0">
-        <v>0.89260470939860181</v>
+        <v>0.89260470939860182</v>
       </c>
       <c r="BT29" s="0">
         <v>1.4924107521410992</v>
@@ -10687,7 +10688,7 @@
         <v>0.1679186920017674</v>
       </c>
       <c r="D30" s="0">
-        <v>0.27593366663934626</v>
+        <v>0.27593366663934627</v>
       </c>
       <c r="E30" s="0">
         <v>0.23050805220695864</v>
@@ -10711,7 +10712,7 @@
         <v>0.24705435195743042</v>
       </c>
       <c r="L30" s="0">
-        <v>0.23086485526549438</v>
+        <v>0.23086485526549439</v>
       </c>
       <c r="M30" s="0">
         <v>0.18018018018018003</v>
@@ -10720,7 +10721,7 @@
         <v>0.22845275181723759</v>
       </c>
       <c r="O30" s="0">
-        <v>0.098872849515522956</v>
+        <v>0.098872849515522957</v>
       </c>
       <c r="P30" s="0">
         <v>0.2161178410965135</v>
@@ -10795,7 +10796,7 @@
         <v>1.1739264751312934</v>
       </c>
       <c r="AN30" s="0">
-        <v>1.260321599304649</v>
+        <v>1.2603215993046491</v>
       </c>
       <c r="AO30" s="0">
         <v>1.2584269662921337</v>
@@ -10948,7 +10949,7 @@
         <v>0.68523430592396051</v>
       </c>
       <c r="CM30" s="0">
-        <v>0.96888392025339964</v>
+        <v>0.96888392025339965</v>
       </c>
       <c r="CN30" s="0">
         <v>1.1725293132328298</v>
@@ -11014,7 +11015,7 @@
         <v>0.17825311942958985</v>
       </c>
       <c r="DI30" s="0">
-        <v>2.4922118380062281</v>
+        <v>2.4922118380062282</v>
       </c>
       <c r="DJ30" s="0">
         <v>0.54200542005420016</v>
@@ -11052,7 +11053,7 @@
         <v>0.34696609567521758</v>
       </c>
       <c r="E31" s="0">
-        <v>0.23985297324237589</v>
+        <v>0.2398529732423759</v>
       </c>
       <c r="F31" s="0">
         <v>0.24963415683911488</v>
@@ -11073,7 +11074,7 @@
         <v>0.076016723679209364</v>
       </c>
       <c r="L31" s="0">
-        <v>0.23086485526549438</v>
+        <v>0.23086485526549439</v>
       </c>
       <c r="M31" s="0">
         <v>0.33264033264033238</v>
@@ -11166,7 +11167,7 @@
         <v>1.5011037527593805</v>
       </c>
       <c r="AQ31" s="0">
-        <v>1.373390557939913</v>
+        <v>1.3733905579399131</v>
       </c>
       <c r="AR31" s="0">
         <v>1.221183800623052</v>
@@ -11193,7 +11194,7 @@
         <v>1.1324570273003023</v>
       </c>
       <c r="AZ31" s="0">
-        <v>1.2659009509694938</v>
+        <v>1.2659009509694939</v>
       </c>
       <c r="BA31" s="0">
         <v>0.55573031351578017</v>
@@ -11211,7 +11212,7 @@
         <v>1.1251758087201114</v>
       </c>
       <c r="BF31" s="0">
-        <v>0.93016798556157076</v>
+        <v>0.93016798556157077</v>
       </c>
       <c r="BG31" s="0">
         <v>1.0782501540357354</v>
@@ -11253,10 +11254,10 @@
         <v>0.99761702815137843</v>
       </c>
       <c r="BT31" s="0">
-        <v>1.2465021622996681</v>
+        <v>1.2465021622996682</v>
       </c>
       <c r="BU31" s="0">
-        <v>1.2744793285669866</v>
+        <v>1.2744793285669867</v>
       </c>
       <c r="BV31" s="0">
         <v>0.63882063882063833</v>
@@ -11268,7 +11269,7 @@
         <v>1.2901416351142887</v>
       </c>
       <c r="BY31" s="0">
-        <v>0.85005574136008843</v>
+        <v>0.85005574136008844</v>
       </c>
       <c r="BZ31" s="0">
         <v>1.2506582411795673</v>
@@ -11286,10 +11287,10 @@
         <v>1.3076923076923064</v>
       </c>
       <c r="CE31" s="0">
-        <v>0.82539682539682468</v>
+        <v>0.82539682539682469</v>
       </c>
       <c r="CF31" s="0">
-        <v>0.80598733448474313</v>
+        <v>0.80598733448474314</v>
       </c>
       <c r="CG31" s="0">
         <v>1.2645512025054648</v>
@@ -11394,7 +11395,7 @@
         <v>3.4505208333333304</v>
       </c>
       <c r="DO31" s="0">
-        <v>0.40453074433656921</v>
+        <v>0.40453074433656922</v>
       </c>
       <c r="DP31" s="0">
         <v>2.8169014084507018</v>
@@ -11414,7 +11415,7 @@
         <v>0.34969811217659852</v>
       </c>
       <c r="E32" s="0">
-        <v>0.31772731520418745</v>
+        <v>0.31772731520418746</v>
       </c>
       <c r="F32" s="0">
         <v>0.30702131933086652</v>
@@ -11480,7 +11481,7 @@
         <v>0.43468313886982507</v>
       </c>
       <c r="AA32" s="0">
-        <v>1.3485781295807719</v>
+        <v>1.348578129580772</v>
       </c>
       <c r="AB32" s="0">
         <v>1.1240547721234448</v>
@@ -11498,7 +11499,7 @@
         <v>1.4035087719298285</v>
       </c>
       <c r="AG32" s="0">
-        <v>0.95820129772144524</v>
+        <v>0.95820129772144525</v>
       </c>
       <c r="AH32" s="0">
         <v>1.2448461782429467</v>
@@ -11561,7 +11562,7 @@
         <v>0.8598091643074367</v>
       </c>
       <c r="BB32" s="0">
-        <v>1.3010053222945039</v>
+        <v>1.301005322294504</v>
       </c>
       <c r="BC32" s="0">
         <v>1.3712544438801459</v>
@@ -11678,7 +11679,7 @@
         <v>1.1127063890883018</v>
       </c>
       <c r="CO32" s="0">
-        <v>1.2122013576655239</v>
+        <v>1.212201357665524</v>
       </c>
       <c r="CP32" s="0">
         <v>1.2191709637446571</v>
@@ -11711,7 +11712,7 @@
         <v>3.6631817813437171</v>
       </c>
       <c r="CZ32" s="0">
-        <v>3.6044434086848542</v>
+        <v>3.6044434086848543</v>
       </c>
       <c r="DA32" s="0">
         <v>3.3381364073006816</v>
@@ -11738,7 +11739,7 @@
         <v>1.5151515151515194</v>
       </c>
       <c r="DI32" s="0">
-        <v>3.1152647975077969</v>
+        <v>3.115264797507797</v>
       </c>
       <c r="DJ32" s="0">
         <v>1.6937669376693814</v>
@@ -11773,7 +11774,7 @@
         <v>0.27397260273972573</v>
       </c>
       <c r="D33" s="0">
-        <v>0.4589787722317839</v>
+        <v>0.45897877223178391</v>
       </c>
       <c r="E33" s="0">
         <v>0.3956016571659966</v>
@@ -11923,7 +11924,7 @@
         <v>0.8178672538534123</v>
       </c>
       <c r="BB33" s="0">
-        <v>1.3897102306327604</v>
+        <v>1.3897102306327605</v>
       </c>
       <c r="BC33" s="0">
         <v>1.1638733705772801</v>
@@ -11974,7 +11975,7 @@
         <v>1.1786550415758448</v>
       </c>
       <c r="BS33" s="0">
-        <v>1.147057635607253</v>
+        <v>1.1470576356072531</v>
       </c>
       <c r="BT33" s="0">
         <v>1.2295429492071557</v>
@@ -12028,7 +12029,7 @@
         <v>1.1806873286949178</v>
       </c>
       <c r="CK33" s="0">
-        <v>0.94224492691925565</v>
+        <v>0.94224492691925566</v>
       </c>
       <c r="CL33" s="0">
         <v>0.91575091575091494</v>
@@ -12118,7 +12119,7 @@
         <v>3.7760416666666634</v>
       </c>
       <c r="DO33" s="0">
-        <v>1.3754045307443354</v>
+        <v>1.3754045307443355</v>
       </c>
       <c r="DP33" s="0">
         <v>3.638497652582156</v>
@@ -12141,7 +12142,7 @@
         <v>0.3956016571659966</v>
       </c>
       <c r="F34" s="0">
-        <v>0.33858425870132824</v>
+        <v>0.33858425870132825</v>
       </c>
       <c r="G34" s="0">
         <v>0.38728632478632447</v>
@@ -12234,7 +12235,7 @@
         <v>0.93911248710010242</v>
       </c>
       <c r="AK34" s="0">
-        <v>1.1440457618304722</v>
+        <v>1.1440457618304723</v>
       </c>
       <c r="AL34" s="0">
         <v>1.1349713032823876</v>
@@ -12246,7 +12247,7 @@
         <v>1.434159061277704</v>
       </c>
       <c r="AO34" s="0">
-        <v>1.5131086142322085</v>
+        <v>1.5131086142322086</v>
       </c>
       <c r="AP34" s="0">
         <v>1.074319352465047</v>
@@ -12369,7 +12370,7 @@
         <v>1.3373328333958243</v>
       </c>
       <c r="CD34" s="0">
-        <v>1.3974358974358962</v>
+        <v>1.3974358974358963</v>
       </c>
       <c r="CE34" s="0">
         <v>1.3968253968253954</v>
@@ -12459,7 +12460,7 @@
         <v>3.4552845528455252</v>
       </c>
       <c r="DH34" s="0">
-        <v>2.7629233511586428</v>
+        <v>2.7629233511586429</v>
       </c>
       <c r="DI34" s="0">
         <v>1.2461059190031141</v>
@@ -12497,7 +12498,7 @@
         <v>0.46840477242598283</v>
       </c>
       <c r="D35" s="0">
-        <v>0.58465153129524849</v>
+        <v>0.5846515312952485</v>
       </c>
       <c r="E35" s="0">
         <v>0.57627013051739662</v>
@@ -12653,7 +12654,7 @@
         <v>1.1765701709835779</v>
       </c>
       <c r="BD35" s="0">
-        <v>1.3155190133607388</v>
+        <v>1.3155190133607389</v>
       </c>
       <c r="BE35" s="0">
         <v>1.3595874355368014</v>
@@ -12707,7 +12708,7 @@
         <v>1.3159258107968075</v>
       </c>
       <c r="BV35" s="0">
-        <v>0.93366093366093283</v>
+        <v>0.93366093366093284</v>
       </c>
       <c r="BW35" s="0">
         <v>1.2280701754385952</v>
@@ -12749,7 +12750,7 @@
         <v>1.3976705490848573</v>
       </c>
       <c r="CJ35" s="0">
-        <v>1.3388150959308442</v>
+        <v>1.3388150959308443</v>
       </c>
       <c r="CK35" s="0">
         <v>1.1437491130977711</v>
@@ -12794,7 +12795,7 @@
         <v>3.8670501757750047</v>
       </c>
       <c r="CY35" s="0">
-        <v>2.1233487316638286</v>
+        <v>2.1233487316638287</v>
       </c>
       <c r="CZ35" s="0">
         <v>3.5267614386700812</v>
@@ -12830,7 +12831,7 @@
         <v>4.2005420054200506</v>
       </c>
       <c r="DK35" s="0">
-        <v>2.9588534442903351</v>
+        <v>2.9588534442903352</v>
       </c>
       <c r="DL35" s="0">
         <v>2.3498694516971259</v>
@@ -12842,7 +12843,7 @@
         <v>2.9947916666666639</v>
       </c>
       <c r="DO35" s="0">
-        <v>2.9126213592232983</v>
+        <v>2.9126213592232984</v>
       </c>
       <c r="DP35" s="0">
         <v>4.8122065727699486</v>
@@ -12856,7 +12857,7 @@
         <v>0.58956347215253335</v>
       </c>
       <c r="C36" s="0">
-        <v>0.50964795993518885</v>
+        <v>0.50964795993518886</v>
       </c>
       <c r="D36" s="0">
         <v>0.6529519438297402</v>
@@ -12868,13 +12869,13 @@
         <v>0.47344409055694198</v>
       </c>
       <c r="G36" s="0">
-        <v>0.7478632478632472</v>
+        <v>0.74786324786324721</v>
       </c>
       <c r="H36" s="0">
         <v>0.56514279947522406</v>
       </c>
       <c r="I36" s="0">
-        <v>0.37098560354374271</v>
+        <v>0.37098560354374272</v>
       </c>
       <c r="J36" s="0">
         <v>0.72255259287678175</v>
@@ -12892,7 +12893,7 @@
         <v>0.70612668743509799</v>
       </c>
       <c r="O36" s="0">
-        <v>0.3559422582558826</v>
+        <v>0.35594225825588261</v>
       </c>
       <c r="P36" s="0">
         <v>0.54598191434908672</v>
@@ -12916,7 +12917,7 @@
         <v>1.087622549019607</v>
       </c>
       <c r="W36" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="X36" s="0">
         <v>1.0991093424294098</v>
@@ -12970,7 +12971,7 @@
         <v>0.60843111690569263</v>
       </c>
       <c r="AO36" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="AP36" s="0">
         <v>1.1479028697571734</v>
@@ -13036,7 +13037,7 @@
         <v>1.3782937166021729</v>
       </c>
       <c r="BK36" s="0">
-        <v>1.4355381550930681</v>
+        <v>1.4355381550930682</v>
       </c>
       <c r="BL36" s="0">
         <v>0.56680677620685216</v>
@@ -13045,7 +13046,7 @@
         <v>1.321049887015469</v>
       </c>
       <c r="BN36" s="0">
-        <v>1.366035392735174</v>
+        <v>1.3660353927351741</v>
       </c>
       <c r="BO36" s="0">
         <v>1.2270629291905875</v>
@@ -13230,7 +13231,7 @@
         <v>0.57961034116668042</v>
       </c>
       <c r="G37" s="0">
-        <v>0.64102564102564052</v>
+        <v>0.64102564102564053</v>
       </c>
       <c r="H37" s="0">
         <v>0.67615299222928582</v>
@@ -13365,10 +13366,10 @@
         <v>1.2403100775193787</v>
       </c>
       <c r="AZ37" s="0">
-        <v>1.2659009509694938</v>
+        <v>1.2659009509694939</v>
       </c>
       <c r="BA37" s="0">
-        <v>1.1429170598720761</v>
+        <v>1.1429170598720762</v>
       </c>
       <c r="BB37" s="0">
         <v>1.153163808397397</v>
@@ -13404,7 +13405,7 @@
         <v>0.46490892879887868</v>
       </c>
       <c r="BM37" s="0">
-        <v>1.4195492206964468</v>
+        <v>1.4195492206964469</v>
       </c>
       <c r="BN37" s="0">
         <v>1.2418503570319765</v>
@@ -13476,13 +13477,13 @@
         <v>1.4126080539742767</v>
       </c>
       <c r="CK37" s="0">
-        <v>1.2743011210444148</v>
+        <v>1.2743011210444149</v>
       </c>
       <c r="CL37" s="0">
         <v>1.2567891878236694</v>
       </c>
       <c r="CM37" s="0">
-        <v>1.3787963480529148</v>
+        <v>1.3787963480529149</v>
       </c>
       <c r="CN37" s="0">
         <v>0.77769801387891779</v>
@@ -13521,7 +13522,7 @@
         <v>1.0697787503039136</v>
       </c>
       <c r="CZ37" s="0">
-        <v>1.7866853103394686</v>
+        <v>1.7866853103394687</v>
       </c>
       <c r="DA37" s="0">
         <v>0.33621517771373649</v>
@@ -13592,7 +13593,7 @@
         <v>0.64847493615678597</v>
       </c>
       <c r="G38" s="0">
-        <v>0.93482905982906594</v>
+        <v>0.93482905982906595</v>
       </c>
       <c r="H38" s="0">
         <v>0.56514279947522816</v>
@@ -13658,7 +13659,7 @@
         <v>1.2466789290823708</v>
       </c>
       <c r="AC38" s="0">
-        <v>0.42553191489361974</v>
+        <v>0.42553191489361975</v>
       </c>
       <c r="AD38" s="0">
         <v>1.1658339281465697</v>
@@ -13715,7 +13716,7 @@
         <v>0.97057368941642563</v>
       </c>
       <c r="AV38" s="0">
-        <v>0.99113197704747646</v>
+        <v>0.99113197704747647</v>
       </c>
       <c r="AW38" s="0">
         <v>1.3814137064944474</v>
@@ -13724,7 +13725,7 @@
         <v>1.4990377798035142</v>
       </c>
       <c r="AY38" s="0">
-        <v>1.199865183687234</v>
+        <v>1.1998651836872341</v>
       </c>
       <c r="AZ38" s="0">
         <v>1.2288501914289323</v>
@@ -13826,7 +13827,7 @@
         <v>0.92112838226828464</v>
       </c>
       <c r="CG38" s="0">
-        <v>0.9159132541511612</v>
+        <v>0.91591325415116121</v>
       </c>
       <c r="CH38" s="0">
         <v>1.0202729561415198</v>
@@ -13838,7 +13839,7 @@
         <v>1.3809825005271015</v>
       </c>
       <c r="CK38" s="0">
-        <v>1.2884915566907988</v>
+        <v>1.2884915566907989</v>
       </c>
       <c r="CL38" s="0">
         <v>1.1494252873563293</v>
@@ -13954,7 +13955,7 @@
         <v>0.82063642363203282</v>
       </c>
       <c r="G39" s="0">
-        <v>0.64102564102564052</v>
+        <v>0.64102564102564053</v>
       </c>
       <c r="H39" s="0">
         <v>0.72661217075385942</v>
@@ -13981,7 +13982,7 @@
         <v>0.38889987476105697</v>
       </c>
       <c r="P39" s="0">
-        <v>0.79622362509241817</v>
+        <v>0.79622362509241818</v>
       </c>
       <c r="Q39" s="0">
         <v>1.4403292181069944</v>
@@ -14059,7 +14060,7 @@
         <v>1.0786516853932575</v>
       </c>
       <c r="AP39" s="0">
-        <v>0.8682855040470927</v>
+        <v>0.86828550404709271</v>
       </c>
       <c r="AQ39" s="0">
         <v>1.0443490701001421</v>
@@ -14131,10 +14132,10 @@
         <v>1.1819920041717356</v>
       </c>
       <c r="BN39" s="0">
-        <v>1.366035392735174</v>
+        <v>1.3660353927351741</v>
       </c>
       <c r="BO39" s="0">
-        <v>1.3283800517843058</v>
+        <v>1.3283800517843059</v>
       </c>
       <c r="BP39" s="0">
         <v>1.3227513227513215</v>
@@ -14194,7 +14195,7 @@
         <v>0.94960469943906989</v>
       </c>
       <c r="CI39" s="0">
-        <v>1.2090959511924559</v>
+        <v>1.209095951192456</v>
       </c>
       <c r="CJ39" s="0">
         <v>1.2017710309930414</v>
@@ -14287,7 +14288,7 @@
         <v>3.4188034188034155</v>
       </c>
       <c r="DN39" s="0">
-        <v>0.7161458333333327</v>
+        <v>0.71614583333333271</v>
       </c>
       <c r="DO39" s="0">
         <v>4.0453074433656919</v>
@@ -14310,7 +14311,7 @@
         <v>0.92888561046908635</v>
       </c>
       <c r="E40" s="0">
-        <v>0.8223530511167173</v>
+        <v>0.82235305111671731</v>
       </c>
       <c r="F40" s="0">
         <v>0.80628963300909517</v>
@@ -14325,7 +14326,7 @@
         <v>0.5980066445182719</v>
       </c>
       <c r="J40" s="0">
-        <v>1.208517168616918</v>
+        <v>1.2085171686169181</v>
       </c>
       <c r="K40" s="0">
         <v>0.85518814139110522</v>
@@ -14394,7 +14395,7 @@
         <v>0.77192982456140291</v>
       </c>
       <c r="AG40" s="0">
-        <v>0.26407122378149966</v>
+        <v>0.26407122378149967</v>
       </c>
       <c r="AH40" s="0">
         <v>1.1893434823977156</v>
@@ -14421,13 +14422,13 @@
         <v>1.1235955056179765</v>
       </c>
       <c r="AP40" s="0">
-        <v>0.8682855040470927</v>
+        <v>0.86828550404709271</v>
       </c>
       <c r="AQ40" s="0">
         <v>0.82975679542203074</v>
       </c>
       <c r="AR40" s="0">
-        <v>1.3084112149532698</v>
+        <v>1.3084112149532699</v>
       </c>
       <c r="AS40" s="0">
         <v>1.1243386243386233</v>
@@ -14481,7 +14482,7 @@
         <v>0.32275416890801478</v>
       </c>
       <c r="BJ40" s="0">
-        <v>1.2161415146489762</v>
+        <v>1.2161415146489763</v>
       </c>
       <c r="BK40" s="0">
         <v>1.3119032900611294</v>
@@ -14625,7 +14626,7 @@
         <v>0.20944095376188157</v>
       </c>
       <c r="DF40" s="0">
-        <v>1.3974096796182673</v>
+        <v>1.3974096796182674</v>
       </c>
       <c r="DG40" s="0">
         <v>0.40650406504065006</v>
@@ -14840,13 +14841,13 @@
         <v>0.34024988844265924</v>
       </c>
       <c r="BI41" s="0">
-        <v>0.37296037296037265</v>
+        <v>0.37296037296037266</v>
       </c>
       <c r="BJ41" s="0">
         <v>1.1719181868435589</v>
       </c>
       <c r="BK41" s="0">
-        <v>1.3874579298028697</v>
+        <v>1.3874579298028698</v>
       </c>
       <c r="BL41" s="0">
         <v>0.22927015666794018</v>
@@ -14882,7 +14883,7 @@
         <v>1.212121212121211</v>
       </c>
       <c r="BW41" s="0">
-        <v>0.97953216374268925</v>
+        <v>0.97953216374268926</v>
       </c>
       <c r="BX41" s="0">
         <v>0.85541999719534356</v>
@@ -14915,13 +14916,13 @@
         <v>0.79182178100809486</v>
       </c>
       <c r="CH41" s="0">
-        <v>0.71551609911222946</v>
+        <v>0.71551609911222947</v>
       </c>
       <c r="CI41" s="0">
         <v>1.0870770937326668</v>
       </c>
       <c r="CJ41" s="0">
-        <v>1.1279780729496089</v>
+        <v>1.127978072949609</v>
       </c>
       <c r="CK41" s="0">
         <v>1.4332340002838075</v>
@@ -15014,7 +15015,7 @@
         <v>0.26041666666666646</v>
       </c>
       <c r="DO41" s="0">
-        <v>2.9126213592232983</v>
+        <v>2.9126213592232984</v>
       </c>
       <c r="DP41" s="0">
         <v>0.35211267605633773</v>
@@ -15052,10 +15053,10 @@
         <v>1.1189973783489984</v>
       </c>
       <c r="K42" s="0">
-        <v>1.0072215887495239</v>
+        <v>1.007221588749524</v>
       </c>
       <c r="L42" s="0">
-        <v>1.1188066062866266</v>
+        <v>1.1188066062866267</v>
       </c>
       <c r="M42" s="0">
         <v>1.191961191961191</v>
@@ -15076,7 +15077,7 @@
         <v>1.2855831037649208</v>
       </c>
       <c r="S42" s="0">
-        <v>1.0727222067428241</v>
+        <v>1.0727222067428242</v>
       </c>
       <c r="T42" s="0">
         <v>0.65560335996721919</v>
@@ -15133,13 +15134,13 @@
         <v>1.3000520020800821</v>
       </c>
       <c r="AL42" s="0">
-        <v>1.3671245244083305</v>
+        <v>1.3671245244083306</v>
       </c>
       <c r="AM42" s="0">
         <v>0.8341056533827611</v>
       </c>
       <c r="AN42" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO42" s="0">
         <v>0.94382022471910032</v>
@@ -15169,7 +15170,7 @@
         <v>1.3096519555077133</v>
       </c>
       <c r="AX42" s="0">
-        <v>1.4281373442722562</v>
+        <v>1.4281373442722563</v>
       </c>
       <c r="AY42" s="0">
         <v>1.1796427367711484</v>
@@ -15178,7 +15179,7 @@
         <v>0.79041620353217168</v>
       </c>
       <c r="BA42" s="0">
-        <v>1.3840830449826977</v>
+        <v>1.3840830449826978</v>
       </c>
       <c r="BB42" s="0">
         <v>0.84762467967671917</v>
@@ -15277,7 +15278,7 @@
         <v>0.60863913017786397</v>
       </c>
       <c r="CH42" s="0">
-        <v>0.62276401219027377</v>
+        <v>0.62276401219027378</v>
       </c>
       <c r="CI42" s="0">
         <v>1.1869107043815852</v>
@@ -15387,7 +15388,7 @@
         <v>1.0868252626494375</v>
       </c>
       <c r="B43" s="0">
-        <v>1.0829570162234476</v>
+        <v>1.0829570162234477</v>
       </c>
       <c r="C43" s="0">
         <v>0.99572838415083131</v>
@@ -15396,7 +15397,7 @@
         <v>1.1638390295877379</v>
       </c>
       <c r="E43" s="0">
-        <v>1.0653209980375657</v>
+        <v>1.0653209980375658</v>
       </c>
       <c r="F43" s="0">
         <v>1.0846173710940852</v>
@@ -15513,7 +15514,7 @@
         <v>0.74391988555078614</v>
       </c>
       <c r="AR43" s="0">
-        <v>1.0965732087227404</v>
+        <v>1.0965732087227405</v>
       </c>
       <c r="AS43" s="0">
         <v>0.99206349206349109</v>
@@ -15543,7 +15544,7 @@
         <v>1.1219461046450656</v>
       </c>
       <c r="BB43" s="0">
-        <v>0.70963926670609045</v>
+        <v>0.70963926670609046</v>
       </c>
       <c r="BC43" s="0">
         <v>0.96918909768071693</v>
@@ -15630,7 +15631,7 @@
         <v>0.80769230769230693</v>
       </c>
       <c r="CE43" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="CF43" s="0">
         <v>1.0362694300518125</v>
@@ -15788,7 +15789,7 @@
         <v>1.1734164070612658</v>
       </c>
       <c r="O44" s="0">
-        <v>0.76461670292004424</v>
+        <v>0.76461670292004425</v>
       </c>
       <c r="P44" s="0">
         <v>1.2113973724620362</v>
@@ -15920,13 +15921,13 @@
         <v>1.1939469665417177</v>
       </c>
       <c r="BG44" s="0">
-        <v>0.90573012939001762</v>
+        <v>0.90573012939001763</v>
       </c>
       <c r="BH44" s="0">
         <v>0.1729138777331547</v>
       </c>
       <c r="BI44" s="0">
-        <v>0.16854939931862994</v>
+        <v>0.16854939931862995</v>
       </c>
       <c r="BJ44" s="0">
         <v>0.98765432098765349</v>
@@ -16007,19 +16008,19 @@
         <v>0.83194675540765317</v>
       </c>
       <c r="CJ44" s="0">
-        <v>1.1279780729496089</v>
+        <v>1.127978072949609</v>
       </c>
       <c r="CK44" s="0">
         <v>1.2941677309493391</v>
       </c>
       <c r="CL44" s="0">
-        <v>1.2915245673866353</v>
+        <v>1.2915245673866354</v>
       </c>
       <c r="CM44" s="0">
         <v>0.78256008943543809</v>
       </c>
       <c r="CN44" s="0">
-        <v>0.40679588418281853</v>
+        <v>0.40679588418281854</v>
       </c>
       <c r="CO44" s="0">
         <v>0.90804901701489826</v>
@@ -16225,7 +16226,7 @@
         <v>0.6178560395427859</v>
       </c>
       <c r="AN45" s="0">
-        <v>0.17383746197305502</v>
+        <v>0.17383746197305503</v>
       </c>
       <c r="AO45" s="0">
         <v>0.80898876404494313</v>
@@ -16261,7 +16262,7 @@
         <v>1.0313447927199182</v>
       </c>
       <c r="AZ45" s="0">
-        <v>0.57428677287884355</v>
+        <v>0.57428677287884356</v>
       </c>
       <c r="BA45" s="0">
         <v>1.1534025374855816</v>
@@ -16270,7 +16271,7 @@
         <v>0.68007096392666999</v>
       </c>
       <c r="BC45" s="0">
-        <v>0.8549178940240385</v>
+        <v>0.85491789402403851</v>
       </c>
       <c r="BD45" s="0">
         <v>0.64405618362452832</v>
@@ -16282,7 +16283,7 @@
         <v>1.1384145494932658</v>
       </c>
       <c r="BG45" s="0">
-        <v>0.90573012939001762</v>
+        <v>0.90573012939001763</v>
       </c>
       <c r="BH45" s="0">
         <v>0.15060240963855406</v>
@@ -16327,7 +16328,7 @@
         <v>0.84965288571132447</v>
       </c>
       <c r="BV45" s="0">
-        <v>1.3104013104013092</v>
+        <v>1.3104013104013093</v>
       </c>
       <c r="BW45" s="0">
         <v>0.57017543859649078</v>
@@ -16378,7 +16379,7 @@
         <v>1.1115321460149037</v>
       </c>
       <c r="CM45" s="0">
-        <v>0.80119247251723424</v>
+        <v>0.80119247251723425</v>
       </c>
       <c r="CN45" s="0">
         <v>0.23929169657812852</v>
@@ -16473,7 +16474,7 @@
         <v>1.3806706114398513</v>
       </c>
       <c r="B46" s="0">
-        <v>1.1498578357584956</v>
+        <v>1.1498578357584957</v>
       </c>
       <c r="C46" s="0">
         <v>1.2078362056267569</v>
@@ -16488,10 +16489,10 @@
         <v>1.1907836217038326</v>
       </c>
       <c r="G46" s="0">
-        <v>1.3221153846153932</v>
+        <v>1.3221153846153933</v>
       </c>
       <c r="H46" s="0">
-        <v>1.2110202845897748</v>
+        <v>1.2110202845897749</v>
       </c>
       <c r="I46" s="0">
         <v>1.1406423034330084</v>
@@ -16506,7 +16507,7 @@
         <v>1.2431184514295943</v>
       </c>
       <c r="M46" s="0">
-        <v>1.5800415800415903</v>
+        <v>1.5800415800415904</v>
       </c>
       <c r="N46" s="0">
         <v>1.1526479750778891</v>
@@ -16536,19 +16537,19 @@
         <v>0.68933823529412208</v>
       </c>
       <c r="W46" s="0">
-        <v>0.68376068376068821</v>
+        <v>0.68376068376068822</v>
       </c>
       <c r="X46" s="0">
         <v>0.37900322152738547</v>
       </c>
       <c r="Y46" s="0">
-        <v>1.6771488469601787</v>
+        <v>1.6771488469601788</v>
       </c>
       <c r="Z46" s="0">
         <v>1.1439029970258596</v>
       </c>
       <c r="AA46" s="0">
-        <v>0.41043682204632342</v>
+        <v>0.41043682204632343</v>
       </c>
       <c r="AB46" s="0">
         <v>0.57224606580830129</v>
@@ -16614,7 +16615,7 @@
         <v>0.3129890453834136</v>
       </c>
       <c r="AW46" s="0">
-        <v>1.0405453893075058</v>
+        <v>1.0405453893075059</v>
       </c>
       <c r="AX46" s="0">
         <v>1.0229919983794253</v>
@@ -16689,7 +16690,7 @@
         <v>0.9325458501709728</v>
       </c>
       <c r="BV46" s="0">
-        <v>1.2285012285012364</v>
+        <v>1.2285012285012365</v>
       </c>
       <c r="BW46" s="0">
         <v>0.70175438596491679</v>
@@ -16719,7 +16720,7 @@
         <v>1.2063492063492143</v>
       </c>
       <c r="CF46" s="0">
-        <v>1.3241220495106591</v>
+        <v>1.3241220495106592</v>
       </c>
       <c r="CG46" s="0">
         <v>0.36045618389174733</v>
@@ -16850,7 +16851,7 @@
         <v>1.3399902441823752</v>
       </c>
       <c r="G47" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="H47" s="0">
         <v>1.1605611060651921</v>
@@ -16871,7 +16872,7 @@
         <v>1.3582813582813571</v>
       </c>
       <c r="N47" s="0">
-        <v>1.3187954309449625</v>
+        <v>1.3187954309449626</v>
       </c>
       <c r="O47" s="0">
         <v>0.95577087865005517</v>
@@ -16934,7 +16935,7 @@
         <v>1.0149064383127171</v>
       </c>
       <c r="AI47" s="0">
-        <v>0.21283064761325612</v>
+        <v>0.21283064761325613</v>
       </c>
       <c r="AJ47" s="0">
         <v>0.092879256965944193</v>
@@ -16949,7 +16950,7 @@
         <v>0.74142724745134314</v>
       </c>
       <c r="AN47" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO47" s="0">
         <v>0.71910112359550493</v>
@@ -17051,7 +17052,7 @@
         <v>0.68386695679204157</v>
       </c>
       <c r="BV47" s="0">
-        <v>1.3267813267813255</v>
+        <v>1.3267813267813256</v>
       </c>
       <c r="BW47" s="0">
         <v>0.68713450292397604</v>
@@ -17075,7 +17076,7 @@
         <v>0.49993750781152313</v>
       </c>
       <c r="CD47" s="0">
-        <v>0.42307692307692268</v>
+        <v>0.42307692307692269</v>
       </c>
       <c r="CE47" s="0">
         <v>0.95238095238095155</v>
@@ -17263,7 +17264,7 @@
         <v>0.54700854700854651</v>
       </c>
       <c r="X48" s="0">
-        <v>0.36005306045101348</v>
+        <v>0.36005306045101349</v>
       </c>
       <c r="Y48" s="0">
         <v>0.91719077568134089</v>
@@ -17296,7 +17297,7 @@
         <v>0.76910878528385596</v>
       </c>
       <c r="AI48" s="0">
-        <v>0.25336981858720969</v>
+        <v>0.2533698185872097</v>
       </c>
       <c r="AJ48" s="0">
         <v>0.10319917440660466</v>
@@ -17305,7 +17306,7 @@
         <v>0.90632196716440006</v>
       </c>
       <c r="AL48" s="0">
-        <v>0.98665118978525745</v>
+        <v>0.98665118978525746</v>
       </c>
       <c r="AM48" s="0">
         <v>0.55607043558850744</v>
@@ -17362,7 +17363,7 @@
         <v>0.36313806097978729</v>
       </c>
       <c r="BE48" s="0">
-        <v>0.90639162369120096</v>
+        <v>0.90639162369120097</v>
       </c>
       <c r="BF48" s="0">
         <v>0.97181729834790964</v>
@@ -17371,7 +17372,7 @@
         <v>0.68391866913123778</v>
       </c>
       <c r="BH48" s="0">
-        <v>0.066934404283801804</v>
+        <v>0.066934404283801805</v>
       </c>
       <c r="BI48" s="0">
         <v>0.060964676349291681</v>
@@ -17556,7 +17557,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>1.304190315179325</v>
+        <v>1.3041903151793251</v>
       </c>
       <c r="B49" s="0">
         <v>1.333835089479845</v>
@@ -17775,7 +17776,7 @@
         <v>0.54916588954512446</v>
       </c>
       <c r="BV49" s="0">
-        <v>1.0483210483210474</v>
+        <v>1.0483210483210475</v>
       </c>
       <c r="BW49" s="0">
         <v>0.51169590643274809</v>
@@ -17796,7 +17797,7 @@
         <v>0.31496062992125956</v>
       </c>
       <c r="CC49" s="0">
-        <v>0.24996875390576156</v>
+        <v>0.24996875390576157</v>
       </c>
       <c r="CD49" s="0">
         <v>0.49999999999999956</v>
@@ -17957,7 +17958,7 @@
         <v>1.2335412335412326</v>
       </c>
       <c r="N50" s="0">
-        <v>1.4537902388369663</v>
+        <v>1.4537902388369664</v>
       </c>
       <c r="O50" s="0">
         <v>1.1798826708852403</v>
@@ -17975,7 +17976,7 @@
         <v>1.2863378842760276</v>
       </c>
       <c r="T50" s="0">
-        <v>1.2702315099364871</v>
+        <v>1.2702315099364872</v>
       </c>
       <c r="U50" s="0">
         <v>0.63208774865216533</v>
@@ -18047,7 +18048,7 @@
         <v>0.34334763948497826</v>
       </c>
       <c r="AR50" s="0">
-        <v>0.41121495327102769</v>
+        <v>0.4112149532710277</v>
       </c>
       <c r="AS50" s="0">
         <v>0.79365079365079294</v>
@@ -18304,7 +18305,7 @@
         <v>1.1302855989504481</v>
       </c>
       <c r="I51" s="0">
-        <v>1.22923588039867</v>
+        <v>1.2292358803986701</v>
       </c>
       <c r="J51" s="0">
         <v>1.1445744612826898</v>
@@ -18358,7 +18359,7 @@
         <v>0.66346373827499372</v>
       </c>
       <c r="AA51" s="0">
-        <v>0.23453532688361164</v>
+        <v>0.23453532688361165</v>
       </c>
       <c r="AB51" s="0">
         <v>0.36787247087676239</v>
@@ -18493,7 +18494,7 @@
         <v>0.4685164990508498</v>
       </c>
       <c r="BT51" s="0">
-        <v>0.12295429492071556</v>
+        <v>0.12295429492071557</v>
       </c>
       <c r="BU51" s="0">
         <v>0.54916588954512446</v>
@@ -18514,13 +18515,13 @@
         <v>0.30279094260136885</v>
       </c>
       <c r="CA51" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB51" s="0">
         <v>0.47244094488188931</v>
       </c>
       <c r="CC51" s="0">
-        <v>0.24996875390576156</v>
+        <v>0.24996875390576157</v>
       </c>
       <c r="CD51" s="0">
         <v>0.25641025641025622</v>
@@ -19091,7 +19092,7 @@
         <v>0.023640661938534261</v>
       </c>
       <c r="AD53" s="0">
-        <v>0.071377587437544548</v>
+        <v>0.071377587437544549</v>
       </c>
       <c r="AE53" s="0">
         <v>1.2295081967213104</v>
@@ -19151,7 +19152,7 @@
         <v>0.45748116254036558</v>
       </c>
       <c r="AX53" s="0">
-        <v>0.37475944495087576</v>
+        <v>0.37475944495087577</v>
       </c>
       <c r="AY53" s="0">
         <v>0.33704078193461379</v>
@@ -19238,7 +19239,7 @@
         <v>0.26329647182727728</v>
       </c>
       <c r="CA53" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB53" s="0">
         <v>0.47244094488188931</v>
@@ -19256,13 +19257,13 @@
         <v>0.92112838226827776</v>
       </c>
       <c r="CG53" s="0">
-        <v>0.13000059091177676</v>
+        <v>0.13000059091177677</v>
       </c>
       <c r="CH53" s="0">
         <v>0.079501788790247704</v>
       </c>
       <c r="CI53" s="0">
-        <v>0.26622296173044901</v>
+        <v>0.26622296173044902</v>
       </c>
       <c r="CJ53" s="0">
         <v>0.35842293906810008</v>
@@ -19393,7 +19394,7 @@
         <v>1.2181616832779614</v>
       </c>
       <c r="J54" s="0">
-        <v>1.1126031076155753</v>
+        <v>1.1126031076155754</v>
       </c>
       <c r="K54" s="0">
         <v>1.3873052071455707</v>
@@ -19411,7 +19412,7 @@
         <v>1.4237690330235304</v>
       </c>
       <c r="P54" s="0">
-        <v>1.1602115679918092</v>
+        <v>1.1602115679918093</v>
       </c>
       <c r="Q54" s="0">
         <v>1.3374485596707806</v>
@@ -19447,7 +19448,7 @@
         <v>0.1465845793022573</v>
       </c>
       <c r="AB54" s="0">
-        <v>0.20437359493153467</v>
+        <v>0.20437359493153468</v>
       </c>
       <c r="AC54" s="0">
         <v>0.047281323877068522</v>
@@ -19510,7 +19511,7 @@
         <v>0.096877561666293979</v>
       </c>
       <c r="AW54" s="0">
-        <v>0.39468963042698207</v>
+        <v>0.39468963042698208</v>
       </c>
       <c r="AX54" s="0">
         <v>0.32411627671427096</v>
@@ -19534,7 +19535,7 @@
         <v>0.11647824597464874</v>
       </c>
       <c r="BE54" s="0">
-        <v>0.48445069542115909</v>
+        <v>0.4844506954211591</v>
       </c>
       <c r="BF54" s="0">
         <v>0.59697348327085886</v>
@@ -19600,7 +19601,7 @@
         <v>0.15797788309636637</v>
       </c>
       <c r="CA54" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB54" s="0">
         <v>0.4199475065616794</v>
@@ -19630,7 +19631,7 @@
         <v>0.3057136833227912</v>
       </c>
       <c r="CK54" s="0">
-        <v>0.53923655456222463</v>
+        <v>0.53923655456222464</v>
       </c>
       <c r="CL54" s="0">
         <v>0.55892383478590324</v>
@@ -19749,7 +19750,7 @@
         <v>1.1217948717948791</v>
       </c>
       <c r="H55" s="0">
-        <v>1.190836613179945</v>
+        <v>1.1908366131799451</v>
       </c>
       <c r="I55" s="0">
         <v>1.2569213732004512</v>
@@ -19797,7 +19798,7 @@
         <v>0.11965811965812044</v>
       </c>
       <c r="X55" s="0">
-        <v>0.075800644305477088</v>
+        <v>0.075800644305477089</v>
       </c>
       <c r="Y55" s="0">
         <v>0.52410901467505577</v>
@@ -19872,7 +19873,7 @@
         <v>0.022356360384529542</v>
       </c>
       <c r="AW55" s="0">
-        <v>0.42160028704700669</v>
+        <v>0.4216002870470067</v>
       </c>
       <c r="AX55" s="0">
         <v>0.29373037577231026</v>
@@ -19971,7 +19972,7 @@
         <v>0.11248593925759354</v>
       </c>
       <c r="CD55" s="0">
-        <v>0.12820512820512905</v>
+        <v>0.12820512820512906</v>
       </c>
       <c r="CE55" s="0">
         <v>0.57142857142857517</v>
@@ -20231,10 +20232,10 @@
         <v>0.69238377843719023</v>
       </c>
       <c r="AV56" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW56" s="0">
-        <v>0.39468963042698207</v>
+        <v>0.39468963042698208</v>
       </c>
       <c r="AX56" s="0">
         <v>0.32411627671427096</v>
@@ -20282,7 +20283,7 @@
         <v>0.0063686154629983387</v>
       </c>
       <c r="BM56" s="0">
-        <v>0.15644011819920028</v>
+        <v>0.15644011819920029</v>
       </c>
       <c r="BN56" s="0">
         <v>0.30011383628272764</v>
@@ -20309,7 +20310,7 @@
         <v>0.176147549476738</v>
       </c>
       <c r="BV56" s="0">
-        <v>0.76986076986076923</v>
+        <v>0.76986076986076924</v>
       </c>
       <c r="BW56" s="0">
         <v>0.20467836257309924</v>
@@ -20476,7 +20477,7 @@
         <v>1.0192754061963862</v>
       </c>
       <c r="I57" s="0">
-        <v>1.22923588039867</v>
+        <v>1.2292358803986701</v>
       </c>
       <c r="J57" s="0">
         <v>0.80567811241127885</v>
@@ -20494,7 +20495,7 @@
         <v>1.1526479750778806</v>
       </c>
       <c r="O57" s="0">
-        <v>1.2392063805945543</v>
+        <v>1.2392063805945544</v>
       </c>
       <c r="P57" s="0">
         <v>0.9895922197577196</v>
@@ -20593,7 +20594,7 @@
         <v>0.61201780415430207</v>
       </c>
       <c r="AV57" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW57" s="0">
         <v>0.17043415859346953</v>
@@ -20623,7 +20624,7 @@
         <v>0.28129395218002784</v>
       </c>
       <c r="BF57" s="0">
-        <v>0.29154518950437291</v>
+        <v>0.29154518950437292</v>
       </c>
       <c r="BG57" s="0">
         <v>0.12939001848428824</v>
@@ -20668,7 +20669,7 @@
         <v>0.021199016365640616</v>
       </c>
       <c r="BU57" s="0">
-        <v>0.15542430836182763</v>
+        <v>0.15542430836182764</v>
       </c>
       <c r="BV57" s="0">
         <v>0.62244062244062193</v>
@@ -20692,7 +20693,7 @@
         <v>0.15748031496062978</v>
       </c>
       <c r="CC57" s="0">
-        <v>0.024996875390576156</v>
+        <v>0.024996875390576157</v>
       </c>
       <c r="CD57" s="0">
         <v>0.12820512820512811</v>
@@ -20934,7 +20935,7 @@
         <v>0</v>
       </c>
       <c r="AO58" s="0">
-        <v>0.089887640449438116</v>
+        <v>0.089887640449438117</v>
       </c>
       <c r="AP58" s="0">
         <v>0</v>
@@ -21021,13 +21022,13 @@
         <v>0.3709021296960992</v>
       </c>
       <c r="BR58" s="0">
-        <v>0.17760555421005877</v>
+        <v>0.17760555421005878</v>
       </c>
       <c r="BS58" s="0">
         <v>0.10097338341613141</v>
       </c>
       <c r="BT58" s="0">
-        <v>0.016959213092512491</v>
+        <v>0.016959213092512492</v>
       </c>
       <c r="BU58" s="0">
         <v>0.14506268780437248</v>
@@ -21042,7 +21043,7 @@
         <v>0.04206983592763984</v>
       </c>
       <c r="BY58" s="0">
-        <v>0.34838350055741329</v>
+        <v>0.3483835005574133</v>
       </c>
       <c r="BZ58" s="0">
         <v>0.078988941548183186</v>
@@ -21078,7 +21079,7 @@
         <v>0.13704406493780297</v>
       </c>
       <c r="CK58" s="0">
-        <v>0.33205619412515935</v>
+        <v>0.33205619412515936</v>
       </c>
       <c r="CL58" s="0">
         <v>0.366300366300366</v>
@@ -21176,13 +21177,13 @@
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>0.78492935635792715</v>
+        <v>0.78492935635792716</v>
       </c>
       <c r="B59" s="0">
-        <v>0.62719518314099298</v>
+        <v>0.62719518314099299</v>
       </c>
       <c r="C59" s="0">
-        <v>0.84548534393872365</v>
+        <v>0.84548534393872366</v>
       </c>
       <c r="D59" s="0">
         <v>0.74857252137802843</v>
@@ -21194,7 +21195,7 @@
         <v>0.84646064675332056</v>
       </c>
       <c r="G59" s="0">
-        <v>0.64102564102564052</v>
+        <v>0.64102564102564053</v>
       </c>
       <c r="H59" s="0">
         <v>1.0192754061963862</v>
@@ -21212,7 +21213,7 @@
         <v>0.95897709110282281</v>
       </c>
       <c r="M59" s="0">
-        <v>0.65142065142065086</v>
+        <v>0.65142065142065087</v>
       </c>
       <c r="N59" s="0">
         <v>0.83073727933540942</v>
@@ -21242,7 +21243,7 @@
         <v>0.061274509803921511</v>
       </c>
       <c r="W59" s="0">
-        <v>0.085470085470085388</v>
+        <v>0.085470085470085389</v>
       </c>
       <c r="X59" s="0">
         <v>0</v>
@@ -21317,10 +21318,10 @@
         <v>0.50074183976261089</v>
       </c>
       <c r="AV59" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW59" s="0">
-        <v>0.18837459634015052</v>
+        <v>0.18837459634015053</v>
       </c>
       <c r="AX59" s="0">
         <v>0.16205813835713548</v>
@@ -21359,7 +21360,7 @@
         <v>0</v>
       </c>
       <c r="BJ59" s="0">
-        <v>0.081076100976598411</v>
+        <v>0.081076100976598412</v>
       </c>
       <c r="BK59" s="0">
         <v>0.10302905419328243</v>
@@ -21413,10 +21414,10 @@
         <v>0.10025062656641595</v>
       </c>
       <c r="CB59" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC59" s="0">
-        <v>0.024996875390576156</v>
+        <v>0.024996875390576157</v>
       </c>
       <c r="CD59" s="0">
         <v>0.076923076923076858</v>
@@ -21452,7 +21453,7 @@
         <v>0</v>
       </c>
       <c r="CO59" s="0">
-        <v>0.066120074054482877</v>
+        <v>0.066120074054482878</v>
       </c>
       <c r="CP59" s="0">
         <v>0.0079945636966862466</v>
@@ -21547,7 +21548,7 @@
         <v>0.79245838856974449</v>
       </c>
       <c r="D60" s="0">
-        <v>0.62016774581318423</v>
+        <v>0.62016774581318424</v>
       </c>
       <c r="E60" s="0">
         <v>0.75382363019032428</v>
@@ -21646,7 +21647,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="0">
-        <v>0.059430948666518039</v>
+        <v>0.05943094866651804</v>
       </c>
       <c r="AL60" s="0">
         <v>0.1354227123234667</v>
@@ -21679,7 +21680,7 @@
         <v>0.43273986152324395</v>
       </c>
       <c r="AV60" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW60" s="0">
         <v>0.11661284535342652</v>
@@ -21760,7 +21761,7 @@
         <v>0.36036036036036007</v>
       </c>
       <c r="BW60" s="0">
-        <v>0.04385964912280698</v>
+        <v>0.043859649122806981</v>
       </c>
       <c r="BX60" s="0">
         <v>0.014023278642546615</v>
@@ -21942,7 +21943,7 @@
         <v>0.70612668743509799</v>
       </c>
       <c r="O61" s="0">
-        <v>0.87667259903763683</v>
+        <v>0.87667259903763684</v>
       </c>
       <c r="P61" s="0">
         <v>0.63697890007393443</v>
@@ -22038,7 +22039,7 @@
         <v>0</v>
       </c>
       <c r="AU61" s="0">
-        <v>0.40182987141444076</v>
+        <v>0.40182987141444077</v>
       </c>
       <c r="AV61" s="0">
         <v>0.014904240256352921</v>
@@ -22065,7 +22066,7 @@
         <v>0.071948535635686414</v>
       </c>
       <c r="BD61" s="0">
-        <v>0.020554984583761544</v>
+        <v>0.020554984583761545</v>
       </c>
       <c r="BE61" s="0">
         <v>0.14064697609001392</v>
@@ -22107,7 +22108,7 @@
         <v>0.15553960277578355</v>
       </c>
       <c r="BR61" s="0">
-        <v>0.024218939210462562</v>
+        <v>0.024218939210462563</v>
       </c>
       <c r="BS61" s="0">
         <v>0.036350418029807312</v>
@@ -22265,7 +22266,7 @@
         <v>0.656120436340216</v>
       </c>
       <c r="B62" s="0">
-        <v>0.57701956848971347</v>
+        <v>0.57701956848971348</v>
       </c>
       <c r="C62" s="0">
         <v>0.6893504197967294</v>
@@ -22286,7 +22287,7 @@
         <v>0.61560197799979766</v>
       </c>
       <c r="I62" s="0">
-        <v>0.8914728682170534</v>
+        <v>0.89147286821705341</v>
       </c>
       <c r="J62" s="0">
         <v>0.34529061960483376</v>
@@ -22295,7 +22296,7 @@
         <v>0.57012542759407026</v>
       </c>
       <c r="L62" s="0">
-        <v>0.58604155567394733</v>
+        <v>0.58604155567394734</v>
       </c>
       <c r="M62" s="0">
         <v>0.52668052668052623</v>
@@ -22400,10 +22401,10 @@
         <v>0</v>
       </c>
       <c r="AU62" s="0">
-        <v>0.24109792284866446</v>
+        <v>0.24109792284866447</v>
       </c>
       <c r="AV62" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW62" s="0">
         <v>0.062791532113383508</v>
@@ -22469,7 +22470,7 @@
         <v>0.13161043311797069</v>
       </c>
       <c r="BR62" s="0">
-        <v>0.024218939210462562</v>
+        <v>0.024218939210462563</v>
       </c>
       <c r="BS62" s="0">
         <v>0.04846722403974308</v>
@@ -22520,7 +22521,7 @@
         <v>0.013250298131707952</v>
       </c>
       <c r="CI62" s="0">
-        <v>0.044370493621741502</v>
+        <v>0.044370493621741503</v>
       </c>
       <c r="CJ62" s="0">
         <v>0.063251106894370593</v>
@@ -22633,10 +22634,10 @@
         <v>0.60980998674326503</v>
       </c>
       <c r="D63" s="0">
-        <v>0.45078272272764824</v>
+        <v>0.45078272272764825</v>
       </c>
       <c r="E63" s="0">
-        <v>0.50151076223406243</v>
+        <v>0.50151076223406244</v>
       </c>
       <c r="F63" s="0">
         <v>0.5423086855470467</v>
@@ -22663,7 +22664,7 @@
         <v>0.4573804573804604</v>
       </c>
       <c r="N63" s="0">
-        <v>0.56074766355140548</v>
+        <v>0.56074766355140549</v>
       </c>
       <c r="O63" s="0">
         <v>0.8898556456397132</v>
@@ -23022,7 +23023,7 @@
         <v>0.65707689575563788</v>
       </c>
       <c r="M64" s="0">
-        <v>0.44352044352044317</v>
+        <v>0.44352044352044318</v>
       </c>
       <c r="N64" s="0">
         <v>0.43613707165109</v>
@@ -23181,7 +23182,7 @@
         <v>0.017382235355466697</v>
       </c>
       <c r="BN64" s="0">
-        <v>0.031046258925799416</v>
+        <v>0.031046258925799417</v>
       </c>
       <c r="BO64" s="0">
         <v>0.12383203872565564</v>
@@ -23223,7 +23224,7 @@
         <v>0.050125313283207976</v>
       </c>
       <c r="CB64" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC64" s="0">
         <v>0</v>
@@ -23375,13 +23376,13 @@
         <v>0.66998892580287872</v>
       </c>
       <c r="J65" s="0">
-        <v>0.31971353667114238</v>
+        <v>0.31971353667114239</v>
       </c>
       <c r="K65" s="0">
         <v>0.22805017103762809</v>
       </c>
       <c r="L65" s="0">
-        <v>0.58604155567394733</v>
+        <v>0.58604155567394734</v>
       </c>
       <c r="M65" s="0">
         <v>0.30492030492030464</v>
@@ -23459,7 +23460,7 @@
         <v>0.02971547433325902</v>
       </c>
       <c r="AL65" s="0">
-        <v>0.051589604694653977</v>
+        <v>0.051589604694653978</v>
       </c>
       <c r="AM65" s="0">
         <v>0.030892801977139301</v>
@@ -23516,7 +23517,7 @@
         <v>0.0068516615279205148</v>
       </c>
       <c r="BE65" s="0">
-        <v>0.031254883575558653</v>
+        <v>0.031254883575558654</v>
       </c>
       <c r="BF65" s="0">
         <v>0.041649312786338995</v>
@@ -23555,7 +23556,7 @@
         <v>0</v>
       </c>
       <c r="BR65" s="0">
-        <v>0.024218939210462562</v>
+        <v>0.024218939210462563</v>
       </c>
       <c r="BS65" s="0">
         <v>0.01211680600993577</v>
@@ -23585,7 +23586,7 @@
         <v>0.050125313283207976</v>
       </c>
       <c r="CB65" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC65" s="0">
         <v>0</v>
@@ -23719,10 +23720,10 @@
         <v>0.3358373840035348</v>
       </c>
       <c r="D66" s="0">
-        <v>0.25134551812692923</v>
+        <v>0.25134551812692924</v>
       </c>
       <c r="E66" s="0">
-        <v>0.32395726256113105</v>
+        <v>0.32395726256113106</v>
       </c>
       <c r="F66" s="0">
         <v>0.36153912369802843</v>
@@ -23752,7 +23753,7 @@
         <v>0.29075804776739328</v>
       </c>
       <c r="O66" s="0">
-        <v>0.55368795728692854</v>
+        <v>0.55368795728692855</v>
       </c>
       <c r="P66" s="0">
         <v>0.28436558039014931</v>
@@ -23911,7 +23912,7 @@
         <v>0.045029832263874782</v>
       </c>
       <c r="BP66" s="0">
-        <v>0.02204585537918869</v>
+        <v>0.022045855379188691</v>
       </c>
       <c r="BQ66" s="0">
         <v>0.047858339315625706</v>
@@ -23947,7 +23948,7 @@
         <v>0</v>
       </c>
       <c r="CB66" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC66" s="0">
         <v>0.012498437695288078</v>
@@ -24180,7 +24181,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="0">
-        <v>0.02228660574994443</v>
+        <v>0.022286605749944431</v>
       </c>
       <c r="AL67" s="0">
         <v>0.01289740117366359</v>
@@ -24282,7 +24283,7 @@
         <v>0.0080729797368209125</v>
       </c>
       <c r="BS67" s="0">
-        <v>0.012116806009935858</v>
+        <v>0.012116806009935859</v>
       </c>
       <c r="BT67" s="0">
         <v>0.0042398032731281541</v>
@@ -24336,7 +24337,7 @@
         <v>0.010541851149061844</v>
       </c>
       <c r="CK67" s="0">
-        <v>0.056761742585497744</v>
+        <v>0.056761742585497745</v>
       </c>
       <c r="CL67" s="0">
         <v>0.044208664898320357</v>
@@ -24446,7 +24447,7 @@
         <v>0.18304510559243625</v>
       </c>
       <c r="E68" s="0">
-        <v>0.21804815749306738</v>
+        <v>0.21804815749306739</v>
       </c>
       <c r="F68" s="0">
         <v>0.31562939370462567</v>
@@ -24455,7 +24456,7 @@
         <v>0.17361111111110966</v>
       </c>
       <c r="H68" s="0">
-        <v>0.24220405691795135</v>
+        <v>0.24220405691795136</v>
       </c>
       <c r="I68" s="0">
         <v>0.54817275747507843</v>
@@ -24632,7 +24633,7 @@
         <v>0.020697505950532789</v>
       </c>
       <c r="BO68" s="0">
-        <v>0.056287290329843052</v>
+        <v>0.056287290329843053</v>
       </c>
       <c r="BP68" s="0">
         <v>0.014697236919459018</v>
@@ -24695,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="CJ68" s="0">
-        <v>0.031625553447185067</v>
+        <v>0.031625553447185068</v>
       </c>
       <c r="CK68" s="0">
         <v>0.017028522775649074</v>
@@ -24814,13 +24815,13 @@
         <v>0.26971966371122957</v>
       </c>
       <c r="G69" s="0">
-        <v>0.066773504273504702</v>
+        <v>0.066773504273504703</v>
       </c>
       <c r="H69" s="0">
         <v>0.22202038550812536</v>
       </c>
       <c r="I69" s="0">
-        <v>0.44296788482835286</v>
+        <v>0.44296788482835287</v>
       </c>
       <c r="J69" s="0">
         <v>0.16625103906899527</v>
@@ -24829,16 +24830,16 @@
         <v>0.11402508551881489</v>
       </c>
       <c r="L69" s="0">
-        <v>0.19534718522465055</v>
+        <v>0.19534718522465056</v>
       </c>
       <c r="M69" s="0">
         <v>0.23562023562023718</v>
       </c>
       <c r="N69" s="0">
-        <v>0.29075804776739544</v>
+        <v>0.29075804776739545</v>
       </c>
       <c r="O69" s="0">
-        <v>0.47458967767451365</v>
+        <v>0.47458967767451366</v>
       </c>
       <c r="P69" s="0">
         <v>0.18199397144969692</v>
@@ -24934,7 +24935,7 @@
         <v>0</v>
       </c>
       <c r="AU69" s="0">
-        <v>0.068001978239367405</v>
+        <v>0.068001978239367406</v>
       </c>
       <c r="AV69" s="0">
         <v>0</v>
@@ -25203,7 +25204,7 @@
         <v>0.3493507349548452</v>
       </c>
       <c r="P70" s="0">
-        <v>0.14787010180287657</v>
+        <v>0.14787010180287658</v>
       </c>
       <c r="Q70" s="0">
         <v>0</v>
@@ -25224,7 +25225,7 @@
         <v>0</v>
       </c>
       <c r="W70" s="0">
-        <v>0.017094017094016953</v>
+        <v>0.017094017094016954</v>
       </c>
       <c r="X70" s="0">
         <v>0</v>
@@ -25356,7 +25357,7 @@
         <v>0.020697505950532789</v>
       </c>
       <c r="BO70" s="0">
-        <v>0.056287290329843052</v>
+        <v>0.056287290329843053</v>
       </c>
       <c r="BP70" s="0">
         <v>0.0073486184597295091</v>
@@ -25538,7 +25539,7 @@
         <v>0.11764368310808948</v>
       </c>
       <c r="G71" s="0">
-        <v>0.066773504273504702</v>
+        <v>0.066773504273504703</v>
       </c>
       <c r="H71" s="0">
         <v>0.13119386416389228</v>
@@ -25607,7 +25608,7 @@
         <v>0</v>
       </c>
       <c r="AD71" s="0">
-        <v>0.023792529145848357</v>
+        <v>0.023792529145848358</v>
       </c>
       <c r="AE71" s="0">
         <v>0.068306010928962199</v>
@@ -25891,7 +25892,7 @@
         <v>0.12667550449256043</v>
       </c>
       <c r="D72" s="0">
-        <v>0.079228478540009722</v>
+        <v>0.079228478540009723</v>
       </c>
       <c r="E72" s="0">
         <v>0.093449210354171738</v>
@@ -25909,7 +25910,7 @@
         <v>0.2325581395348818</v>
       </c>
       <c r="J72" s="0">
-        <v>0.051154165867382403</v>
+        <v>0.051154165867382404</v>
       </c>
       <c r="K72" s="0">
         <v>0.076016723679208795</v>
@@ -26508,7 +26509,7 @@
         <v>0</v>
       </c>
       <c r="CK73" s="0">
-        <v>0.0056761742585497744</v>
+        <v>0.0056761742585497745</v>
       </c>
       <c r="CL73" s="0">
         <v>0.012631047113805817</v>
@@ -26663,7 +26664,7 @@
         <v>0.037150552614469833</v>
       </c>
       <c r="T74" s="0">
-        <v>0.13658403332650298</v>
+        <v>0.13658403332650299</v>
       </c>
       <c r="U74" s="0">
         <v>0</v>
@@ -27351,13 +27352,13 @@
         <v>0.040064102564102824</v>
       </c>
       <c r="H76" s="0">
-        <v>0.04036734281965916</v>
+        <v>0.040367342819659161</v>
       </c>
       <c r="I76" s="0">
         <v>0.077519379844961739</v>
       </c>
       <c r="J76" s="0">
-        <v>0.04475989513396026</v>
+        <v>0.044759895133960261</v>
       </c>
       <c r="K76" s="0">
         <v>0.01900418091980248</v>
@@ -28422,7 +28423,7 @@
         <v>0.012543903662819766</v>
       </c>
       <c r="C79" s="0">
-        <v>0.0088378258948297993</v>
+        <v>0.0088378258948297994</v>
       </c>
       <c r="D79" s="0">
         <v>0.010928066005518582</v>
@@ -28431,7 +28432,7 @@
         <v>0.018689842070834347</v>
       </c>
       <c r="F79" s="0">
-        <v>0.037301655619637573</v>
+        <v>0.037301655619637574</v>
       </c>
       <c r="G79" s="0">
         <v>0</v>
@@ -28440,7 +28441,7 @@
         <v>0.040367342819658557</v>
       </c>
       <c r="I79" s="0">
-        <v>0.0387596899224803</v>
+        <v>0.038759689922480301</v>
       </c>
       <c r="J79" s="0">
         <v>0.0063942707334228004</v>
@@ -28458,7 +28459,7 @@
         <v>0</v>
       </c>
       <c r="O79" s="0">
-        <v>0.046140663107243698</v>
+        <v>0.046140663107243699</v>
       </c>
       <c r="P79" s="0">
         <v>0.011374623215605889</v>
@@ -28778,7 +28779,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>0.016101115002214009</v>
+        <v>0.01610111500221401</v>
       </c>
       <c r="B80" s="0">
         <v>0.0083626024418799669</v>
@@ -29161,7 +29162,7 @@
         <v>0.013354700854700743</v>
       </c>
       <c r="H81" s="0">
-        <v>0.020183671409829278</v>
+        <v>0.020183671409829279</v>
       </c>
       <c r="I81" s="0">
         <v>0.033222591362125964</v>
@@ -29173,7 +29174,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="0">
-        <v>0.017758835020422511</v>
+        <v>0.017758835020422512</v>
       </c>
       <c r="M81" s="0">
         <v>0</v>
@@ -29870,7 +29871,7 @@
         <v>0.0041813012209399219</v>
       </c>
       <c r="C83" s="0">
-        <v>0.0088378258948297993</v>
+        <v>0.0088378258948297994</v>
       </c>
       <c r="D83" s="0">
         <v>0.0054640330027592911</v>
@@ -30852,7 +30853,7 @@
         <v>0</v>
       </c>
       <c r="CK85" s="0">
-        <v>0.0056761742585497744</v>
+        <v>0.0056761742585497745</v>
       </c>
       <c r="CL85" s="0">
         <v>0</v>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0010_ses-01_pet_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0010_ses-01_pet_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
